--- a/sheets/대금율보/검수/금잔디.xlsx
+++ b/sheets/대금율보/검수/금잔디.xlsx
@@ -6430,7 +6430,7 @@
       </c>
       <c r="D4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 汰
 汰</t>
         </is>
@@ -6455,7 +6455,7 @@
       <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-–‹
+–
 南∧</t>
         </is>
       </c>
@@ -6478,7 +6478,7 @@
       </c>
       <c r="L4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太‹
+          <t xml:space="preserve">太
 –汰c
 南∧</t>
         </is>
@@ -6511,7 +6511,7 @@
       <c r="R4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-–‹
+–
 南∧</t>
         </is>
       </c>
@@ -6579,7 +6579,7 @@
       <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林·
-林林‹
+林林
 –
 林</t>
         </is>
@@ -6643,7 +6643,7 @@
       <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-–‹
+–
 南</t>
         </is>
       </c>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="J6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 潢∧
 汰∧</t>
         </is>
@@ -6682,7 +6682,7 @@
       <c r="O6" s="24"/>
       <c r="P6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞‹
+          <t xml:space="preserve">㳞
 㳞汰
 淋</t>
         </is>
@@ -6734,7 +6734,7 @@
       <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–‹
+–
 潕</t>
         </is>
       </c>
@@ -6914,7 +6914,7 @@
       <c r="R8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-–‹
+–
 林汰</t>
         </is>
       </c>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="L9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰‹
+          <t xml:space="preserve">汰
 –汰c
 南∧</t>
         </is>
@@ -7037,7 +7037,7 @@
       </c>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 潢
 汰∧</t>
         </is>
@@ -7337,7 +7337,7 @@
       </c>
       <c r="R12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 淋
 淋</t>
         </is>
@@ -7364,7 +7364,7 @@
       </c>
       <c r="D13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰‹
+          <t xml:space="preserve">汰
 –汰c
 汰c</t>
         </is>
@@ -7577,7 +7577,7 @@
       <c r="D15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–‹
+–
 汰</t>
         </is>
       </c>
@@ -7589,7 +7589,7 @@
       <c r="F15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-–‹
+–
 汰</t>
         </is>
       </c>
@@ -7645,7 +7645,7 @@
       <c r="P15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-–‹
+–
 太</t>
         </is>
       </c>
@@ -7762,7 +7762,7 @@
       </c>
       <c r="R16" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 汰
 –
 ㄱ</t>
@@ -7779,7 +7779,7 @@
       <c r="B17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林·
-林林‹
+林林
 –
 林</t>
         </is>

--- a/sheets/대금율보/검수/금잔디.xlsx
+++ b/sheets/대금율보/검수/금잔디.xlsx
@@ -6259,30 +6259,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="13.46" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="13.46" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="13.46" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="13.46" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="13.46" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="13.46" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="13.46" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="13.46" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="13.46" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="111.11" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
       <c r="R2" s="20"/>
       <c r="S2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="124.34" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -6414,7 +6414,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="124.34" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -6521,7 +6521,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="124.34" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -6610,7 +6610,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="124.34" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -6705,7 +6705,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="124.34" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="124.34" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="124.34" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="124.34" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="124.34" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="124.34" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -7348,7 +7348,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="124.34" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -7459,7 +7459,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="124.34" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -7564,7 +7564,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="124.34" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -7667,7 +7667,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="124.34" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -7774,7 +7774,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="124.34" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -7862,7 +7862,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="124.34" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -7965,6 +7965,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="67"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="36"/>
 </worksheet>
 </file>